--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733272</v>
       </c>
       <c r="B2" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129733266</v>
       </c>
       <c r="B3" t="n">
-        <v>80046</v>
+        <v>80047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733273</v>
+        <v>129733276</v>
       </c>
       <c r="B4" t="n">
-        <v>91587</v>
+        <v>80085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543865</v>
+        <v>543738</v>
       </c>
       <c r="R4" t="n">
-        <v>6778660</v>
+        <v>6778508</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733276</v>
+        <v>129733267</v>
       </c>
       <c r="B5" t="n">
-        <v>80084</v>
+        <v>79332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6459</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543738</v>
+        <v>544097</v>
       </c>
       <c r="R5" t="n">
-        <v>6778508</v>
+        <v>6778637</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733267</v>
+        <v>129733273</v>
       </c>
       <c r="B6" t="n">
-        <v>79331</v>
+        <v>91588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544097</v>
+        <v>543865</v>
       </c>
       <c r="R6" t="n">
-        <v>6778637</v>
+        <v>6778660</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1183,7 +1183,7 @@
         <v>129733270</v>
       </c>
       <c r="B7" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129733284</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,50 +1378,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733281</v>
+        <v>129733268</v>
       </c>
       <c r="B9" t="n">
-        <v>57732</v>
+        <v>80054</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skålsjöboåsen, Hls</t>
+          <t>Skåsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543657</v>
+        <v>544132</v>
       </c>
       <c r="R9" t="n">
-        <v>6778495</v>
+        <v>6778602</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,10 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733268</v>
+        <v>129733289</v>
       </c>
       <c r="B10" t="n">
-        <v>80053</v>
+        <v>80054</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544132</v>
+        <v>543763</v>
       </c>
       <c r="R10" t="n">
-        <v>6778602</v>
+        <v>6778485</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1585,45 +1580,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733289</v>
+        <v>129733281</v>
       </c>
       <c r="B11" t="n">
-        <v>80053</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skåsjöboåsen, Hls</t>
+          <t>Skålsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543763</v>
+        <v>543657</v>
       </c>
       <c r="R11" t="n">
-        <v>6778485</v>
+        <v>6778495</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1689,7 +1689,7 @@
         <v>129733275</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129733280</v>
       </c>
       <c r="B13" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>129733288</v>
       </c>
       <c r="B14" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>129733271</v>
       </c>
       <c r="B15" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>129733278</v>
       </c>
       <c r="B16" t="n">
-        <v>80046</v>
+        <v>80047</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129733265</v>
       </c>
       <c r="B17" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>129733283</v>
       </c>
       <c r="B18" t="n">
-        <v>80053</v>
+        <v>80054</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129733274</v>
       </c>
       <c r="B19" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733272</v>
       </c>
       <c r="B2" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129733266</v>
       </c>
       <c r="B3" t="n">
-        <v>80047</v>
+        <v>80052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129733276</v>
       </c>
       <c r="B4" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129733267</v>
       </c>
       <c r="B5" t="n">
-        <v>79332</v>
+        <v>79337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129733273</v>
       </c>
       <c r="B6" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129733270</v>
       </c>
       <c r="B7" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129733284</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,45 +1378,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733268</v>
+        <v>129733281</v>
       </c>
       <c r="B9" t="n">
-        <v>80054</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skåsjöboåsen, Hls</t>
+          <t>Skålsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544132</v>
+        <v>543657</v>
       </c>
       <c r="R9" t="n">
-        <v>6778602</v>
+        <v>6778495</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1479,10 +1484,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733289</v>
+        <v>129733268</v>
       </c>
       <c r="B10" t="n">
-        <v>80054</v>
+        <v>80059</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1514,10 +1519,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543763</v>
+        <v>544132</v>
       </c>
       <c r="R10" t="n">
-        <v>6778485</v>
+        <v>6778602</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1580,50 +1585,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733281</v>
+        <v>129733289</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>80059</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skålsjöboåsen, Hls</t>
+          <t>Skåsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543657</v>
+        <v>543763</v>
       </c>
       <c r="R11" t="n">
-        <v>6778495</v>
+        <v>6778485</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1689,7 +1689,7 @@
         <v>129733275</v>
       </c>
       <c r="B12" t="n">
-        <v>80141</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129733280</v>
       </c>
       <c r="B13" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>129733288</v>
       </c>
       <c r="B14" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>129733271</v>
       </c>
       <c r="B15" t="n">
-        <v>80141</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>129733278</v>
       </c>
       <c r="B16" t="n">
-        <v>80047</v>
+        <v>80052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129733265</v>
       </c>
       <c r="B17" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>129733283</v>
       </c>
       <c r="B18" t="n">
-        <v>80054</v>
+        <v>80059</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129733274</v>
       </c>
       <c r="B19" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733276</v>
+        <v>129733273</v>
       </c>
       <c r="B4" t="n">
-        <v>80090</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543738</v>
+        <v>543865</v>
       </c>
       <c r="R4" t="n">
-        <v>6778508</v>
+        <v>6778660</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733267</v>
+        <v>129733276</v>
       </c>
       <c r="B5" t="n">
-        <v>79337</v>
+        <v>80090</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6459</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544097</v>
+        <v>543738</v>
       </c>
       <c r="R5" t="n">
-        <v>6778637</v>
+        <v>6778508</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733273</v>
+        <v>129733267</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>79337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543865</v>
+        <v>544097</v>
       </c>
       <c r="R6" t="n">
-        <v>6778660</v>
+        <v>6778637</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129733270</v>
+        <v>129733284</v>
       </c>
       <c r="B7" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,19 +1191,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1211,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544052</v>
+        <v>543724</v>
       </c>
       <c r="R7" t="n">
-        <v>6778672</v>
+        <v>6778502</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1277,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733284</v>
+        <v>129733270</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,23 +1292,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543724</v>
+        <v>544052</v>
       </c>
       <c r="R8" t="n">
-        <v>6778502</v>
+        <v>6778672</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1378,50 +1378,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733281</v>
+        <v>129733268</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>80059</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skålsjöboåsen, Hls</t>
+          <t>Skåsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543657</v>
+        <v>544132</v>
       </c>
       <c r="R9" t="n">
-        <v>6778495</v>
+        <v>6778602</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,7 +1479,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733268</v>
+        <v>129733289</v>
       </c>
       <c r="B10" t="n">
         <v>80059</v>
@@ -1519,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544132</v>
+        <v>543763</v>
       </c>
       <c r="R10" t="n">
-        <v>6778602</v>
+        <v>6778485</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1585,45 +1580,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733289</v>
+        <v>129733281</v>
       </c>
       <c r="B11" t="n">
-        <v>80059</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skåsjöboåsen, Hls</t>
+          <t>Skålsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543763</v>
+        <v>543657</v>
       </c>
       <c r="R11" t="n">
-        <v>6778485</v>
+        <v>6778495</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129733284</v>
+        <v>129733270</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,23 +1191,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1215,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543724</v>
+        <v>544052</v>
       </c>
       <c r="R7" t="n">
-        <v>6778502</v>
+        <v>6778672</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733270</v>
+        <v>129733284</v>
       </c>
       <c r="B8" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,19 +1288,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544052</v>
+        <v>543724</v>
       </c>
       <c r="R8" t="n">
-        <v>6778672</v>
+        <v>6778502</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733273</v>
+        <v>129733267</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>79337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543865</v>
+        <v>544097</v>
       </c>
       <c r="R4" t="n">
-        <v>6778660</v>
+        <v>6778637</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733267</v>
+        <v>129733273</v>
       </c>
       <c r="B6" t="n">
-        <v>79337</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544097</v>
+        <v>543865</v>
       </c>
       <c r="R6" t="n">
-        <v>6778637</v>
+        <v>6778660</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129733270</v>
+        <v>129733284</v>
       </c>
       <c r="B7" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,19 +1191,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1211,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544052</v>
+        <v>543724</v>
       </c>
       <c r="R7" t="n">
-        <v>6778672</v>
+        <v>6778502</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1277,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733284</v>
+        <v>129733270</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,23 +1292,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543724</v>
+        <v>544052</v>
       </c>
       <c r="R8" t="n">
-        <v>6778502</v>
+        <v>6778672</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733272</v>
       </c>
       <c r="B2" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733267</v>
+        <v>129733273</v>
       </c>
       <c r="B4" t="n">
-        <v>79337</v>
+        <v>91597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544097</v>
+        <v>543865</v>
       </c>
       <c r="R4" t="n">
-        <v>6778637</v>
+        <v>6778660</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733273</v>
+        <v>129733267</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>79337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543865</v>
+        <v>544097</v>
       </c>
       <c r="R6" t="n">
-        <v>6778660</v>
+        <v>6778637</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1284,7 +1284,7 @@
         <v>129733270</v>
       </c>
       <c r="B8" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733272</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733273</v>
+        <v>129733276</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
+        <v>80090</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543865</v>
+        <v>543738</v>
       </c>
       <c r="R4" t="n">
-        <v>6778660</v>
+        <v>6778508</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733276</v>
+        <v>129733267</v>
       </c>
       <c r="B5" t="n">
-        <v>80090</v>
+        <v>79337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6459</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543738</v>
+        <v>544097</v>
       </c>
       <c r="R5" t="n">
-        <v>6778508</v>
+        <v>6778637</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733267</v>
+        <v>129733273</v>
       </c>
       <c r="B6" t="n">
-        <v>79337</v>
+        <v>91599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544097</v>
+        <v>543865</v>
       </c>
       <c r="R6" t="n">
-        <v>6778637</v>
+        <v>6778660</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129733284</v>
+        <v>129733270</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,23 +1191,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1215,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543724</v>
+        <v>544052</v>
       </c>
       <c r="R7" t="n">
-        <v>6778502</v>
+        <v>6778672</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733270</v>
+        <v>129733284</v>
       </c>
       <c r="B8" t="n">
-        <v>91617</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,19 +1288,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544052</v>
+        <v>543724</v>
       </c>
       <c r="R8" t="n">
-        <v>6778672</v>
+        <v>6778502</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733276</v>
+        <v>129733273</v>
       </c>
       <c r="B4" t="n">
-        <v>80090</v>
+        <v>91599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543738</v>
+        <v>543865</v>
       </c>
       <c r="R4" t="n">
-        <v>6778508</v>
+        <v>6778660</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733267</v>
+        <v>129733276</v>
       </c>
       <c r="B5" t="n">
-        <v>79337</v>
+        <v>80090</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6459</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544097</v>
+        <v>543738</v>
       </c>
       <c r="R5" t="n">
-        <v>6778637</v>
+        <v>6778508</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733273</v>
+        <v>129733267</v>
       </c>
       <c r="B6" t="n">
-        <v>91599</v>
+        <v>79337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543865</v>
+        <v>544097</v>
       </c>
       <c r="R6" t="n">
-        <v>6778660</v>
+        <v>6778637</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129733270</v>
+        <v>129733284</v>
       </c>
       <c r="B7" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,19 +1191,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1211,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544052</v>
+        <v>543724</v>
       </c>
       <c r="R7" t="n">
-        <v>6778672</v>
+        <v>6778502</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1277,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733284</v>
+        <v>129733270</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,23 +1292,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543724</v>
+        <v>544052</v>
       </c>
       <c r="R8" t="n">
-        <v>6778502</v>
+        <v>6778672</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1378,45 +1378,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733268</v>
+        <v>129733281</v>
       </c>
       <c r="B9" t="n">
-        <v>80059</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skåsjöboåsen, Hls</t>
+          <t>Skålsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544132</v>
+        <v>543657</v>
       </c>
       <c r="R9" t="n">
-        <v>6778602</v>
+        <v>6778495</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1479,7 +1484,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733289</v>
+        <v>129733268</v>
       </c>
       <c r="B10" t="n">
         <v>80059</v>
@@ -1514,10 +1519,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543763</v>
+        <v>544132</v>
       </c>
       <c r="R10" t="n">
-        <v>6778485</v>
+        <v>6778602</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1580,50 +1585,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733281</v>
+        <v>129733289</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>80059</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skålsjöboåsen, Hls</t>
+          <t>Skåsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543657</v>
+        <v>543763</v>
       </c>
       <c r="R11" t="n">
-        <v>6778495</v>
+        <v>6778485</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733273</v>
+        <v>129733276</v>
       </c>
       <c r="B4" t="n">
-        <v>91599</v>
+        <v>80090</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543865</v>
+        <v>543738</v>
       </c>
       <c r="R4" t="n">
-        <v>6778660</v>
+        <v>6778508</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733276</v>
+        <v>129733267</v>
       </c>
       <c r="B5" t="n">
-        <v>80090</v>
+        <v>79337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6459</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543738</v>
+        <v>544097</v>
       </c>
       <c r="R5" t="n">
-        <v>6778508</v>
+        <v>6778637</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733267</v>
+        <v>129733273</v>
       </c>
       <c r="B6" t="n">
-        <v>79337</v>
+        <v>91599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544097</v>
+        <v>543865</v>
       </c>
       <c r="R6" t="n">
-        <v>6778637</v>
+        <v>6778660</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733272</v>
       </c>
       <c r="B2" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733276</v>
+        <v>129733273</v>
       </c>
       <c r="B4" t="n">
-        <v>80090</v>
+        <v>91599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543738</v>
+        <v>543865</v>
       </c>
       <c r="R4" t="n">
-        <v>6778508</v>
+        <v>6778660</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733267</v>
+        <v>129733276</v>
       </c>
       <c r="B5" t="n">
-        <v>79337</v>
+        <v>80090</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6459</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544097</v>
+        <v>543738</v>
       </c>
       <c r="R5" t="n">
-        <v>6778637</v>
+        <v>6778508</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733273</v>
+        <v>129733267</v>
       </c>
       <c r="B6" t="n">
-        <v>91599</v>
+        <v>79337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543865</v>
+        <v>544097</v>
       </c>
       <c r="R6" t="n">
-        <v>6778660</v>
+        <v>6778637</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1378,50 +1378,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733281</v>
+        <v>129733268</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>80059</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skålsjöboåsen, Hls</t>
+          <t>Skåsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543657</v>
+        <v>544132</v>
       </c>
       <c r="R9" t="n">
-        <v>6778495</v>
+        <v>6778602</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,7 +1479,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733268</v>
+        <v>129733289</v>
       </c>
       <c r="B10" t="n">
         <v>80059</v>
@@ -1519,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544132</v>
+        <v>543763</v>
       </c>
       <c r="R10" t="n">
-        <v>6778602</v>
+        <v>6778485</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1585,45 +1580,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733289</v>
+        <v>129733281</v>
       </c>
       <c r="B11" t="n">
-        <v>80059</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skåsjöboåsen, Hls</t>
+          <t>Skålsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543763</v>
+        <v>543657</v>
       </c>
       <c r="R11" t="n">
-        <v>6778485</v>
+        <v>6778495</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733273</v>
+        <v>129733267</v>
       </c>
       <c r="B4" t="n">
-        <v>91599</v>
+        <v>79337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543865</v>
+        <v>544097</v>
       </c>
       <c r="R4" t="n">
-        <v>6778660</v>
+        <v>6778637</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733267</v>
+        <v>129733273</v>
       </c>
       <c r="B6" t="n">
-        <v>79337</v>
+        <v>91599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544097</v>
+        <v>543865</v>
       </c>
       <c r="R6" t="n">
-        <v>6778637</v>
+        <v>6778660</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129733284</v>
+        <v>129733270</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,23 +1191,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1215,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543724</v>
+        <v>544052</v>
       </c>
       <c r="R7" t="n">
-        <v>6778502</v>
+        <v>6778672</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733270</v>
+        <v>129733284</v>
       </c>
       <c r="B8" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,19 +1288,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544052</v>
+        <v>543724</v>
       </c>
       <c r="R8" t="n">
-        <v>6778672</v>
+        <v>6778502</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1378,45 +1378,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733268</v>
+        <v>129733281</v>
       </c>
       <c r="B9" t="n">
-        <v>80059</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skåsjöboåsen, Hls</t>
+          <t>Skålsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544132</v>
+        <v>543657</v>
       </c>
       <c r="R9" t="n">
-        <v>6778602</v>
+        <v>6778495</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1479,7 +1484,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733289</v>
+        <v>129733268</v>
       </c>
       <c r="B10" t="n">
         <v>80059</v>
@@ -1514,10 +1519,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543763</v>
+        <v>544132</v>
       </c>
       <c r="R10" t="n">
-        <v>6778485</v>
+        <v>6778602</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1580,50 +1585,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733281</v>
+        <v>129733289</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>80059</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skålsjöboåsen, Hls</t>
+          <t>Skåsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543657</v>
+        <v>543763</v>
       </c>
       <c r="R11" t="n">
-        <v>6778495</v>
+        <v>6778485</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733272</v>
       </c>
       <c r="B2" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129733266</v>
       </c>
       <c r="B3" t="n">
-        <v>80052</v>
+        <v>80055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733267</v>
+        <v>129733273</v>
       </c>
       <c r="B4" t="n">
-        <v>79337</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544097</v>
+        <v>543865</v>
       </c>
       <c r="R4" t="n">
-        <v>6778637</v>
+        <v>6778660</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
         <v>129733276</v>
       </c>
       <c r="B5" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733273</v>
+        <v>129733267</v>
       </c>
       <c r="B6" t="n">
-        <v>91599</v>
+        <v>79340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543865</v>
+        <v>544097</v>
       </c>
       <c r="R6" t="n">
-        <v>6778660</v>
+        <v>6778637</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129733270</v>
+        <v>129733284</v>
       </c>
       <c r="B7" t="n">
-        <v>91619</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,19 +1191,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1211,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544052</v>
+        <v>543724</v>
       </c>
       <c r="R7" t="n">
-        <v>6778672</v>
+        <v>6778502</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1277,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733284</v>
+        <v>129733270</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>91622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,23 +1292,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543724</v>
+        <v>544052</v>
       </c>
       <c r="R8" t="n">
-        <v>6778502</v>
+        <v>6778672</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1378,50 +1378,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733281</v>
+        <v>129733268</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>80062</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skålsjöboåsen, Hls</t>
+          <t>Skåsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543657</v>
+        <v>544132</v>
       </c>
       <c r="R9" t="n">
-        <v>6778495</v>
+        <v>6778602</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,10 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733268</v>
+        <v>129733289</v>
       </c>
       <c r="B10" t="n">
-        <v>80059</v>
+        <v>80062</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544132</v>
+        <v>543763</v>
       </c>
       <c r="R10" t="n">
-        <v>6778602</v>
+        <v>6778485</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1585,45 +1580,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733289</v>
+        <v>129733281</v>
       </c>
       <c r="B11" t="n">
-        <v>80059</v>
+        <v>57734</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skåsjöboåsen, Hls</t>
+          <t>Skålsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543763</v>
+        <v>543657</v>
       </c>
       <c r="R11" t="n">
-        <v>6778485</v>
+        <v>6778495</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1689,7 +1689,7 @@
         <v>129733275</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129733280</v>
       </c>
       <c r="B13" t="n">
-        <v>79113</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>129733288</v>
       </c>
       <c r="B14" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>129733271</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>129733278</v>
       </c>
       <c r="B16" t="n">
-        <v>80052</v>
+        <v>80055</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129733265</v>
       </c>
       <c r="B17" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>129733283</v>
       </c>
       <c r="B18" t="n">
-        <v>80059</v>
+        <v>80062</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129733274</v>
       </c>
       <c r="B19" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733273</v>
+        <v>129733276</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>80093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543865</v>
+        <v>543738</v>
       </c>
       <c r="R4" t="n">
-        <v>6778660</v>
+        <v>6778508</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733276</v>
+        <v>129733267</v>
       </c>
       <c r="B5" t="n">
-        <v>80093</v>
+        <v>79340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6459</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543738</v>
+        <v>544097</v>
       </c>
       <c r="R5" t="n">
-        <v>6778508</v>
+        <v>6778637</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733267</v>
+        <v>129733273</v>
       </c>
       <c r="B6" t="n">
-        <v>79340</v>
+        <v>91602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544097</v>
+        <v>543865</v>
       </c>
       <c r="R6" t="n">
-        <v>6778637</v>
+        <v>6778660</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129733284</v>
+        <v>129733270</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>91622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,23 +1191,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1215,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543724</v>
+        <v>544052</v>
       </c>
       <c r="R7" t="n">
-        <v>6778502</v>
+        <v>6778672</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733270</v>
+        <v>129733284</v>
       </c>
       <c r="B8" t="n">
-        <v>91622</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,19 +1288,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544052</v>
+        <v>543724</v>
       </c>
       <c r="R8" t="n">
-        <v>6778672</v>
+        <v>6778502</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733268</v>
+        <v>129733289</v>
       </c>
       <c r="B9" t="n">
         <v>80062</v>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544132</v>
+        <v>543763</v>
       </c>
       <c r="R9" t="n">
-        <v>6778602</v>
+        <v>6778485</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733289</v>
+        <v>129733268</v>
       </c>
       <c r="B10" t="n">
         <v>80062</v>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543763</v>
+        <v>544132</v>
       </c>
       <c r="R10" t="n">
-        <v>6778485</v>
+        <v>6778602</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733276</v>
+        <v>129733273</v>
       </c>
       <c r="B4" t="n">
-        <v>80093</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543738</v>
+        <v>543865</v>
       </c>
       <c r="R4" t="n">
-        <v>6778508</v>
+        <v>6778660</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733267</v>
+        <v>129733276</v>
       </c>
       <c r="B5" t="n">
-        <v>79340</v>
+        <v>80093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6459</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544097</v>
+        <v>543738</v>
       </c>
       <c r="R5" t="n">
-        <v>6778637</v>
+        <v>6778508</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733273</v>
+        <v>129733267</v>
       </c>
       <c r="B6" t="n">
-        <v>91602</v>
+        <v>79340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543865</v>
+        <v>544097</v>
       </c>
       <c r="R6" t="n">
-        <v>6778660</v>
+        <v>6778637</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733272</v>
       </c>
       <c r="B2" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129733266</v>
       </c>
       <c r="B3" t="n">
-        <v>80055</v>
+        <v>80058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129733273</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129733276</v>
       </c>
       <c r="B5" t="n">
-        <v>80093</v>
+        <v>80096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129733267</v>
       </c>
       <c r="B6" t="n">
-        <v>79340</v>
+        <v>79343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129733270</v>
       </c>
       <c r="B7" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129733284</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,10 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733289</v>
+        <v>129733268</v>
       </c>
       <c r="B9" t="n">
-        <v>80062</v>
+        <v>80065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543763</v>
+        <v>544132</v>
       </c>
       <c r="R9" t="n">
-        <v>6778485</v>
+        <v>6778602</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733268</v>
+        <v>129733289</v>
       </c>
       <c r="B10" t="n">
-        <v>80062</v>
+        <v>80065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544132</v>
+        <v>543763</v>
       </c>
       <c r="R10" t="n">
-        <v>6778602</v>
+        <v>6778485</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1583,7 +1583,7 @@
         <v>129733281</v>
       </c>
       <c r="B11" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>129733275</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129733280</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79119</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>129733288</v>
       </c>
       <c r="B14" t="n">
-        <v>80093</v>
+        <v>80096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>129733271</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>80152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>129733278</v>
       </c>
       <c r="B16" t="n">
-        <v>80055</v>
+        <v>80058</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129733265</v>
       </c>
       <c r="B17" t="n">
-        <v>80093</v>
+        <v>80096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>129733283</v>
       </c>
       <c r="B18" t="n">
-        <v>80062</v>
+        <v>80065</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129733274</v>
       </c>
       <c r="B19" t="n">
-        <v>80093</v>
+        <v>80096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -1378,45 +1378,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733268</v>
+        <v>129733281</v>
       </c>
       <c r="B9" t="n">
-        <v>80065</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skåsjöboåsen, Hls</t>
+          <t>Skålsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544132</v>
+        <v>543657</v>
       </c>
       <c r="R9" t="n">
-        <v>6778602</v>
+        <v>6778495</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1479,7 +1484,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733289</v>
+        <v>129733268</v>
       </c>
       <c r="B10" t="n">
         <v>80065</v>
@@ -1514,10 +1519,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543763</v>
+        <v>544132</v>
       </c>
       <c r="R10" t="n">
-        <v>6778485</v>
+        <v>6778602</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1580,50 +1585,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733281</v>
+        <v>129733289</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>80065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skålsjöboåsen, Hls</t>
+          <t>Skåsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543657</v>
+        <v>543763</v>
       </c>
       <c r="R11" t="n">
-        <v>6778495</v>
+        <v>6778485</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733272</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129733266</v>
       </c>
       <c r="B3" t="n">
-        <v>80058</v>
+        <v>80059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129733273</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129733276</v>
       </c>
       <c r="B5" t="n">
-        <v>80096</v>
+        <v>80097</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129733267</v>
       </c>
       <c r="B6" t="n">
-        <v>79343</v>
+        <v>79344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129733270</v>
+        <v>129733284</v>
       </c>
       <c r="B7" t="n">
-        <v>91625</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,19 +1191,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1211,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544052</v>
+        <v>543724</v>
       </c>
       <c r="R7" t="n">
-        <v>6778672</v>
+        <v>6778502</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1277,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733284</v>
+        <v>129733270</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>91626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,23 +1292,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543724</v>
+        <v>544052</v>
       </c>
       <c r="R8" t="n">
-        <v>6778502</v>
+        <v>6778672</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1487,7 +1487,7 @@
         <v>129733268</v>
       </c>
       <c r="B10" t="n">
-        <v>80065</v>
+        <v>80066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>129733289</v>
       </c>
       <c r="B11" t="n">
-        <v>80065</v>
+        <v>80066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>129733275</v>
       </c>
       <c r="B12" t="n">
-        <v>80152</v>
+        <v>80153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129733280</v>
       </c>
       <c r="B13" t="n">
-        <v>79119</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>129733288</v>
       </c>
       <c r="B14" t="n">
-        <v>80096</v>
+        <v>80097</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>129733271</v>
       </c>
       <c r="B15" t="n">
-        <v>80152</v>
+        <v>80153</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>129733278</v>
       </c>
       <c r="B16" t="n">
-        <v>80058</v>
+        <v>80059</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129733265</v>
       </c>
       <c r="B17" t="n">
-        <v>80096</v>
+        <v>80097</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>129733283</v>
       </c>
       <c r="B18" t="n">
-        <v>80065</v>
+        <v>80066</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129733274</v>
       </c>
       <c r="B19" t="n">
-        <v>80096</v>
+        <v>80097</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129733284</v>
+        <v>129733270</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>91626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,23 +1191,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1215,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543724</v>
+        <v>544052</v>
       </c>
       <c r="R7" t="n">
-        <v>6778502</v>
+        <v>6778672</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733270</v>
+        <v>129733284</v>
       </c>
       <c r="B8" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,19 +1288,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544052</v>
+        <v>543724</v>
       </c>
       <c r="R8" t="n">
-        <v>6778672</v>
+        <v>6778502</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1378,50 +1378,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733281</v>
+        <v>129733268</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>80066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skålsjöboåsen, Hls</t>
+          <t>Skåsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543657</v>
+        <v>544132</v>
       </c>
       <c r="R9" t="n">
-        <v>6778495</v>
+        <v>6778602</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,7 +1479,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733268</v>
+        <v>129733289</v>
       </c>
       <c r="B10" t="n">
         <v>80066</v>
@@ -1519,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544132</v>
+        <v>543763</v>
       </c>
       <c r="R10" t="n">
-        <v>6778602</v>
+        <v>6778485</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1585,45 +1580,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733289</v>
+        <v>129733281</v>
       </c>
       <c r="B11" t="n">
-        <v>80066</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skåsjöboåsen, Hls</t>
+          <t>Skålsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543763</v>
+        <v>543657</v>
       </c>
       <c r="R11" t="n">
-        <v>6778485</v>
+        <v>6778495</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733273</v>
+        <v>129733276</v>
       </c>
       <c r="B4" t="n">
-        <v>91606</v>
+        <v>80097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543865</v>
+        <v>543738</v>
       </c>
       <c r="R4" t="n">
-        <v>6778660</v>
+        <v>6778508</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733276</v>
+        <v>129733267</v>
       </c>
       <c r="B5" t="n">
-        <v>80097</v>
+        <v>79344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6459</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543738</v>
+        <v>544097</v>
       </c>
       <c r="R5" t="n">
-        <v>6778508</v>
+        <v>6778637</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733267</v>
+        <v>129733273</v>
       </c>
       <c r="B6" t="n">
-        <v>79344</v>
+        <v>91606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544097</v>
+        <v>543865</v>
       </c>
       <c r="R6" t="n">
-        <v>6778637</v>
+        <v>6778660</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1378,45 +1378,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733268</v>
+        <v>129733281</v>
       </c>
       <c r="B9" t="n">
-        <v>80066</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skåsjöboåsen, Hls</t>
+          <t>Skålsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544132</v>
+        <v>543657</v>
       </c>
       <c r="R9" t="n">
-        <v>6778602</v>
+        <v>6778495</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1479,7 +1484,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733289</v>
+        <v>129733268</v>
       </c>
       <c r="B10" t="n">
         <v>80066</v>
@@ -1514,10 +1519,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543763</v>
+        <v>544132</v>
       </c>
       <c r="R10" t="n">
-        <v>6778485</v>
+        <v>6778602</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1580,50 +1585,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733281</v>
+        <v>129733289</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>80066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skålsjöboåsen, Hls</t>
+          <t>Skåsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543657</v>
+        <v>543763</v>
       </c>
       <c r="R11" t="n">
-        <v>6778495</v>
+        <v>6778485</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 27178-2025 artfynd.xlsx
+++ b/artfynd/A 27178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733272</v>
       </c>
       <c r="B2" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129733266</v>
       </c>
       <c r="B3" t="n">
-        <v>80059</v>
+        <v>80060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733276</v>
+        <v>129733273</v>
       </c>
       <c r="B4" t="n">
-        <v>80097</v>
+        <v>91623</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543738</v>
+        <v>543865</v>
       </c>
       <c r="R4" t="n">
-        <v>6778508</v>
+        <v>6778660</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733267</v>
+        <v>129733276</v>
       </c>
       <c r="B5" t="n">
-        <v>79344</v>
+        <v>80098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6459</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544097</v>
+        <v>543738</v>
       </c>
       <c r="R5" t="n">
-        <v>6778637</v>
+        <v>6778508</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733273</v>
+        <v>129733267</v>
       </c>
       <c r="B6" t="n">
-        <v>91606</v>
+        <v>79345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543865</v>
+        <v>544097</v>
       </c>
       <c r="R6" t="n">
-        <v>6778660</v>
+        <v>6778637</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1183,7 +1183,7 @@
         <v>129733270</v>
       </c>
       <c r="B7" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129733284</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,50 +1378,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733281</v>
+        <v>129733268</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>80067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skålsjöboåsen, Hls</t>
+          <t>Skåsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543657</v>
+        <v>544132</v>
       </c>
       <c r="R9" t="n">
-        <v>6778495</v>
+        <v>6778602</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,10 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733268</v>
+        <v>129733289</v>
       </c>
       <c r="B10" t="n">
-        <v>80066</v>
+        <v>80067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544132</v>
+        <v>543763</v>
       </c>
       <c r="R10" t="n">
-        <v>6778602</v>
+        <v>6778485</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1585,45 +1580,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733289</v>
+        <v>129733281</v>
       </c>
       <c r="B11" t="n">
-        <v>80066</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skåsjöboåsen, Hls</t>
+          <t>Skålsjöboåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543763</v>
+        <v>543657</v>
       </c>
       <c r="R11" t="n">
-        <v>6778485</v>
+        <v>6778495</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1689,7 +1689,7 @@
         <v>129733275</v>
       </c>
       <c r="B12" t="n">
-        <v>80153</v>
+        <v>80154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129733280</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>129733288</v>
       </c>
       <c r="B14" t="n">
-        <v>80097</v>
+        <v>80098</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>129733271</v>
       </c>
       <c r="B15" t="n">
-        <v>80153</v>
+        <v>80154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>129733278</v>
       </c>
       <c r="B16" t="n">
-        <v>80059</v>
+        <v>80060</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129733265</v>
       </c>
       <c r="B17" t="n">
-        <v>80097</v>
+        <v>80098</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>129733283</v>
       </c>
       <c r="B18" t="n">
-        <v>80066</v>
+        <v>80067</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129733274</v>
       </c>
       <c r="B19" t="n">
-        <v>80097</v>
+        <v>80098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
